--- a/Plantilla Mediciones_completada.xlsx
+++ b/Plantilla Mediciones_completada.xlsx
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B6:F30"/>
+  <dimension ref="B6:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -705,13 +705,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.002600000698294025</v>
+        <v>0.003200000719516538</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.002299999323440716</v>
+        <v>0.002000000677071512</v>
       </c>
     </row>
     <row r="9">
@@ -720,13 +720,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.001700000211712904</v>
+        <v>0.001500000507803634</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.0008999995770864189</v>
+        <v>0.0009000013960758224</v>
       </c>
     </row>
     <row r="10">
@@ -735,13 +735,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.0006999998731771484</v>
+        <v>0.0007999988156370819</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.0006999998731771484</v>
+        <v>0.0006000009307172149</v>
       </c>
     </row>
     <row r="11">
@@ -750,13 +750,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.0005000001692678779</v>
+        <v>0.0003999994078185409</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.0006000000212225132</v>
+        <v>0.0005000001692678779</v>
       </c>
     </row>
     <row r="12">
@@ -765,13 +765,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.0004000003173132427</v>
+        <v>0.0003999994078185409</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.0006000000212225132</v>
+        <v>0.0005999991117278114</v>
       </c>
     </row>
     <row r="13">
@@ -780,13 +780,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.0006000000212225132</v>
+        <v>0.0006000009307172149</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.0005999991117278114</v>
+        <v>0.0005000001692678779</v>
       </c>
     </row>
     <row r="14">
@@ -795,13 +795,13 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.0004000003173132427</v>
+        <v>0.0004000012268079445</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.0005000001692678779</v>
+        <v>0.0005999991117278114</v>
       </c>
     </row>
     <row r="15">
@@ -810,13 +810,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.0004000003173132427</v>
+        <v>0.0004000012268079445</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.0006000000212225132</v>
+        <v>0.0005000001692678779</v>
       </c>
     </row>
     <row r="16">
@@ -825,13 +825,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.0004000003173132427</v>
+        <v>0.0004000012268079445</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.0006000000212225132</v>
+        <v>0.0005000001692678779</v>
       </c>
     </row>
     <row r="17">
@@ -846,7 +846,7 @@
         <v>10</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.0006000000212225132</v>
+        <v>0.0006000009307172149</v>
       </c>
     </row>
     <row r="18">
@@ -855,13 +855,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.0005000001692678779</v>
+        <v>0.0003999994078185409</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.0006000000212225132</v>
+        <v>0.0005000001692678779</v>
       </c>
     </row>
     <row r="19">
@@ -870,13 +870,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.0004000003173132427</v>
+        <v>0.0002999986463692039</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.0005000001692678779</v>
+        <v>0.0005999991117278114</v>
       </c>
     </row>
     <row r="20">
@@ -885,7 +885,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.0003000004653586075</v>
+        <v>0.0003999994078185409</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>13</v>
@@ -906,7 +906,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.0005000001692678779</v>
+        <v>0.0004999983502784744</v>
       </c>
     </row>
     <row r="22">
@@ -921,7 +921,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.0006999998731771484</v>
+        <v>0.0005000001692678779</v>
       </c>
     </row>
     <row r="23">
@@ -936,7 +936,7 @@
         <v>16</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.0006000000212225132</v>
+        <v>0.0005999991117278114</v>
       </c>
     </row>
     <row r="24">
@@ -945,13 +945,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.0004000003173132427</v>
+        <v>0.0003999994078185409</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.0006000000212225132</v>
+        <v>0.0004999983502784744</v>
       </c>
     </row>
     <row r="25">
@@ -960,13 +960,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.0004000003173132427</v>
+        <v>0.0002999986463692039</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.0006000000212225132</v>
+        <v>0.0006000009307172149</v>
       </c>
     </row>
     <row r="26">
@@ -975,13 +975,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.0004000003173132427</v>
+        <v>0.0003999994078185409</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.0006000000212225132</v>
+        <v>0.0005000001692678779</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
@@ -990,13 +990,13 @@
         <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.0005000001692678779</v>
+        <v>0.0003000004653586075</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.0006000000212225132</v>
+        <v>0.0005000001692678779</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
@@ -1006,27 +1006,27 @@
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>0.0006099999154685065</v>
+      </c>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="1" t="n"/>
+      <c r="F28" s="1" t="n">
+        <v>0.0006299999768089037</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B29" s="19" t="n">
-        <v>0.000610000188316917</v>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Desviación Estándar</t>
+        </is>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>0.00068999993345642</v>
+        <v>0.000665622212689929</v>
       </c>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>0.0005543133221313321</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.0003891960336362247</v>
+      <c r="F29" s="1" t="n">
+        <v>0.0003357633186209191</v>
       </c>
     </row>
   </sheetData>
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B6:F30"/>
+  <dimension ref="B6:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -1101,13 +1101,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.009899999895424116</v>
+        <v>0.006599999323952943</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.01309999970544595</v>
+        <v>0.008500001058564521</v>
       </c>
     </row>
     <row r="9">
@@ -1116,13 +1116,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.008099999831756577</v>
+        <v>0.005300000339047983</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.01179999981104629</v>
+        <v>0.007799999366397969</v>
       </c>
     </row>
     <row r="10">
@@ -1131,13 +1131,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.006599999323952943</v>
+        <v>0.004599998646881431</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.01010000050882809</v>
+        <v>0.007399999958579428</v>
       </c>
     </row>
     <row r="11">
@@ -1146,13 +1146,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.00599999930273043</v>
+        <v>0.00419999923906289</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.009700000191514846</v>
+        <v>0.006899999789311551</v>
       </c>
     </row>
     <row r="12">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.005899999450775795</v>
+        <v>0.00419999923906289</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.009700000191514846</v>
+        <v>0.007000000550760888</v>
       </c>
     </row>
     <row r="13">
@@ -1176,13 +1176,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.006399999620043673</v>
+        <v>0.004399998942972161</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.01010000050882809</v>
+        <v>0.007000000550760888</v>
       </c>
     </row>
     <row r="14">
@@ -1191,13 +1191,13 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.006100000064179767</v>
+        <v>0.004399998942972161</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.009999999747378752</v>
+        <v>0.006800000846851617</v>
       </c>
     </row>
     <row r="15">
@@ -1206,13 +1206,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.005899999450775795</v>
+        <v>0.00419999923906289</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.009899999895424116</v>
+        <v>0.00670000008540228</v>
       </c>
     </row>
     <row r="16">
@@ -1221,13 +1221,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.006000000212225132</v>
+        <v>0.00419999923906289</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.009700000191514846</v>
+        <v>0.00670000008540228</v>
       </c>
     </row>
     <row r="17">
@@ -1236,13 +1236,13 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.005900000360270496</v>
+        <v>0.00399999953515362</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.009600000339560211</v>
+        <v>0.006600001142942347</v>
       </c>
     </row>
     <row r="18">
@@ -1251,13 +1251,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.005799999598821159</v>
+        <v>0.004100000296602957</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.009800000043469481</v>
+        <v>0.006600001142942347</v>
       </c>
     </row>
     <row r="19">
@@ -1266,13 +1266,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.005799999598821159</v>
+        <v>0.00399999953515362</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.009499999578110874</v>
+        <v>0.00650000038149301</v>
       </c>
     </row>
     <row r="20">
@@ -1281,13 +1281,13 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.005699999746866524</v>
+        <v>0.00399999953515362</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.009499999578110874</v>
+        <v>0.00670000008540228</v>
       </c>
     </row>
     <row r="21">
@@ -1296,13 +1296,13 @@
         <v>14</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.005700000656361226</v>
+        <v>0.003900000592693686</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.00940000063565094</v>
+        <v>0.006600001142942347</v>
       </c>
     </row>
     <row r="22">
@@ -1311,13 +1311,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.005599999894911889</v>
+        <v>0.003899998773704283</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.009499999578110874</v>
+        <v>0.006600001142942347</v>
       </c>
     </row>
     <row r="23">
@@ -1326,13 +1326,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.005599999894911889</v>
+        <v>0.003799999831244349</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.01840000004449394</v>
+        <v>0.00670000008540228</v>
       </c>
     </row>
     <row r="24">
@@ -1341,13 +1341,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.005599999894911889</v>
+        <v>0.00399999953515362</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.009999999747378752</v>
+        <v>0.00650000038149301</v>
       </c>
     </row>
     <row r="25">
@@ -1356,13 +1356,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.005599999894911889</v>
+        <v>0.003799999831244349</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.009899999895424116</v>
+        <v>0.006599999323952943</v>
       </c>
     </row>
     <row r="26">
@@ -1371,13 +1371,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.005599999894911889</v>
+        <v>0.003899998773704283</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.009899999895424116</v>
+        <v>0.006599999323952943</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
@@ -1386,13 +1386,13 @@
         <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.005500000042957254</v>
+        <v>0.003900000592693686</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.009700000191514846</v>
+        <v>0.006600001142942347</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
@@ -1402,27 +1402,27 @@
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>0.004269999499229016</v>
+      </c>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="1" t="n"/>
+      <c r="F28" s="1" t="n">
+        <v>0.006870000379421981</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B29" s="19" t="n">
-        <v>0.006164999831526075</v>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Desviación Estándar</t>
+        </is>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>0.01046500001393724</v>
+        <v>0.0006473426933359369</v>
       </c>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>0.00104994985071387</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.002062261124952165</v>
+      <c r="F29" s="1" t="n">
+        <v>0.0004995787355440158</v>
       </c>
     </row>
   </sheetData>
@@ -1443,7 +1443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B6:F30"/>
+  <dimension ref="B6:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -1497,13 +1497,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.02170000061596511</v>
+        <v>0.01410000004398171</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.05339999916031957</v>
+        <v>0.04330000047048088</v>
       </c>
     </row>
     <row r="9">
@@ -1512,13 +1512,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.02059999951598002</v>
+        <v>0.01420000080543105</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.03550000019458821</v>
+        <v>0.02570000106061343</v>
       </c>
     </row>
     <row r="10">
@@ -1533,7 +1533,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.03190000006725313</v>
+        <v>0.02250000034109689</v>
       </c>
     </row>
     <row r="11">
@@ -1542,13 +1542,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.01569999949424528</v>
+        <v>0.01109999902837444</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.03120000019407598</v>
+        <v>0.02150000000256114</v>
       </c>
     </row>
     <row r="12">
@@ -1557,13 +1557,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.01570000040373998</v>
+        <v>0.01060000067809597</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.02990000029967632</v>
+        <v>0.02189999941037968</v>
       </c>
     </row>
     <row r="13">
@@ -1572,13 +1572,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.01610000072105322</v>
+        <v>0.02940000013040844</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.03049999941140413</v>
+        <v>0.02170000152545981</v>
       </c>
     </row>
     <row r="14">
@@ -1587,13 +1587,13 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.01549999979033601</v>
+        <v>0.01080000038200524</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.03000000015163096</v>
+        <v>0.0214000010601012</v>
       </c>
     </row>
     <row r="15">
@@ -1602,13 +1602,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.01479999991715886</v>
+        <v>0.01039999915519729</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.02989999939018162</v>
+        <v>0.0211000005947426</v>
       </c>
     </row>
     <row r="16">
@@ -1617,13 +1617,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.01510000038251746</v>
+        <v>0.01059999885910656</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.02979999953822698</v>
+        <v>0.02150000000256114</v>
       </c>
     </row>
     <row r="17">
@@ -1632,13 +1632,13 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.0152000002344721</v>
+        <v>0.01019999945128802</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.02959999983431771</v>
+        <v>0.02119999953720253</v>
       </c>
     </row>
     <row r="18">
@@ -1647,13 +1647,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.02390000008745119</v>
+        <v>0.009999999747378752</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.02969999968627235</v>
+        <v>0.02099999983329326</v>
       </c>
     </row>
     <row r="19">
@@ -1662,13 +1662,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.01439999959984561</v>
+        <v>0.009800000043469481</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.03239999932702631</v>
+        <v>0.02090000089083333</v>
       </c>
     </row>
     <row r="20">
@@ -1677,13 +1677,13 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.01460000021324959</v>
+        <v>0.009999999747378752</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.03149999974993989</v>
+        <v>0.02090000089083333</v>
       </c>
     </row>
     <row r="21">
@@ -1692,13 +1692,13 @@
         <v>14</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.01449999945180025</v>
+        <v>0.009899998985929415</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.02980000044772169</v>
+        <v>0.02049999966402538</v>
       </c>
     </row>
     <row r="22">
@@ -1707,13 +1707,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.01420000080543105</v>
+        <v>0.01019999945128802</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.02920000042649917</v>
+        <v>0.02060000042547472</v>
       </c>
     </row>
     <row r="23">
@@ -1722,13 +1722,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.01479999991715886</v>
+        <v>0.01009999868983869</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.02969999968627235</v>
+        <v>0.02089999907184392</v>
       </c>
     </row>
     <row r="24">
@@ -1737,13 +1737,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.01429999974789098</v>
+        <v>0.01010000050882809</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.02969999968627235</v>
+        <v>0.07120000009308569</v>
       </c>
     </row>
     <row r="25">
@@ -1752,13 +1752,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.01450000036129495</v>
+        <v>0.01010000050882809</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.02920000042649917</v>
+        <v>0.02210000093327835</v>
       </c>
     </row>
     <row r="26">
@@ -1767,13 +1767,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.01439999959984561</v>
+        <v>0.01010000050882809</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.02970000059576705</v>
+        <v>0.02160000076401047</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
@@ -1782,13 +1782,13 @@
         <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.01420000080543105</v>
+        <v>0.01000000156636816</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.02909999966504984</v>
+        <v>0.02129999847966246</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
@@ -1798,27 +1798,27 @@
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>0.01191999990624026</v>
+      </c>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="1" t="n"/>
+      <c r="F28" s="1" t="n">
+        <v>0.02514000025257701</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B29" s="19" t="n">
-        <v>0.01604500007488241</v>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Desviación Estándar</t>
+        </is>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>0.03158499989694974</v>
+        <v>0.004500713476645424</v>
       </c>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>0.002736012281766459</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.005348809337131256</v>
+      <c r="F29" s="1" t="n">
+        <v>0.01192738556793973</v>
       </c>
     </row>
   </sheetData>
@@ -1839,7 +1839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B6:F30"/>
+  <dimension ref="B6:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -1893,13 +1893,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.04030000036436832</v>
+        <v>0.02930000118794851</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.06990000019868603</v>
+        <v>0.05890000102226622</v>
       </c>
     </row>
     <row r="9">
@@ -1908,13 +1908,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.03310000010969816</v>
+        <v>0.0230999994528247</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.05959999998594867</v>
+        <v>0.04399999852466863</v>
       </c>
     </row>
     <row r="10">
@@ -1923,13 +1923,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.03010000000358559</v>
+        <v>0.02099999983329326</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.05609999971056823</v>
+        <v>0.04230000013194513</v>
       </c>
     </row>
     <row r="11">
@@ -1938,13 +1938,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.02829999993991805</v>
+        <v>0.01989999873330817</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.05309999960445566</v>
+        <v>0.04120000085094944</v>
       </c>
     </row>
     <row r="12">
@@ -1953,13 +1953,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.02750000021478627</v>
+        <v>0.01960000008693896</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.05299999975250103</v>
+        <v>0.04150000131630804</v>
       </c>
     </row>
     <row r="13">
@@ -1968,13 +1968,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.02820000008796342</v>
+        <v>0.02029999996011611</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.05289999990054639</v>
+        <v>0.04089999856660143</v>
       </c>
     </row>
     <row r="14">
@@ -1983,13 +1983,13 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.02739999945333693</v>
+        <v>0.02020000101765618</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.05270000019663712</v>
+        <v>0.04059999992023222</v>
       </c>
     </row>
     <row r="15">
@@ -1998,13 +1998,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.02700000004551839</v>
+        <v>0.01990000055229757</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.05260000034468248</v>
+        <v>0.03990000004705507</v>
       </c>
     </row>
     <row r="16">
@@ -2013,13 +2013,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.02619999941089191</v>
+        <v>0.01919999886013102</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.05250000049272785</v>
+        <v>0.04020000051241368</v>
       </c>
     </row>
     <row r="17">
@@ -2028,13 +2028,13 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.02609999955893727</v>
+        <v>0.01919999886013102</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.05280000004859176</v>
+        <v>0.03990000004705507</v>
       </c>
     </row>
     <row r="18">
@@ -2043,13 +2043,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.02620000032038661</v>
+        <v>0.01909999991767108</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.05539999983739108</v>
+        <v>0.0397000003431458</v>
       </c>
     </row>
     <row r="19">
@@ -2058,13 +2058,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.02620000032038661</v>
+        <v>0.01979999979084823</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.05210000017541461</v>
+        <v>0.07890000051702373</v>
       </c>
     </row>
     <row r="20">
@@ -2073,13 +2073,13 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.02630000017234124</v>
+        <v>0.01869999869086314</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.04960000023856992</v>
+        <v>0.0413999987358693</v>
       </c>
     </row>
     <row r="21">
@@ -2088,13 +2088,13 @@
         <v>14</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.02640000002429588</v>
+        <v>0.01879999945231248</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.04960000023856992</v>
+        <v>0.04029999945487361</v>
       </c>
     </row>
     <row r="22">
@@ -2103,13 +2103,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.02670000048965449</v>
+        <v>0.01899999915622175</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.04929999977321131</v>
+        <v>0.04019999869342428</v>
       </c>
     </row>
     <row r="23">
@@ -2118,13 +2118,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.02649999987625051</v>
+        <v>0.01889999839477241</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.04940000053466065</v>
+        <v>0.04019999869342428</v>
       </c>
     </row>
     <row r="24">
@@ -2133,13 +2133,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.02669999958015978</v>
+        <v>0.01890000021376181</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.149000000419619</v>
+        <v>0.04059999992023222</v>
       </c>
     </row>
     <row r="25">
@@ -2148,13 +2148,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.02620000032038661</v>
+        <v>0.01879999945231248</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.05679999958374538</v>
+        <v>0.04040000021632295</v>
       </c>
     </row>
     <row r="26">
@@ -2163,13 +2163,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.02610000046843197</v>
+        <v>0.01859999974840321</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.05619999956252286</v>
+        <v>0.03930000093532726</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
@@ -2178,13 +2178,13 @@
         <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.02610000046843197</v>
+        <v>0.01879999945231248</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.05139999939274276</v>
+        <v>0.03949999882024713</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
@@ -2194,27 +2194,27 @@
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>0.02005499964070623</v>
+      </c>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="1" t="n"/>
+      <c r="F28" s="1" t="n">
+        <v>0.04349499986346927</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B29" s="19" t="n">
-        <v>0.0278800000614865</v>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Desviación Estándar</t>
+        </is>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>0.05869999999958964</v>
+        <v>0.002415623884725289</v>
       </c>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>0.003387531371340314</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.0217511283118088</v>
+      <c r="F29" s="1" t="n">
+        <v>0.009335302507118275</v>
       </c>
     </row>
   </sheetData>
@@ -2235,7 +2235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B6:F30"/>
+  <dimension ref="B6:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -2289,13 +2289,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.04749999970954377</v>
+        <v>0.04210000042803586</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.07719999939581612</v>
+        <v>0.0779999991209479</v>
       </c>
     </row>
     <row r="9">
@@ -2304,13 +2304,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.04309999985707691</v>
+        <v>0.03640000068116933</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.06829999983892776</v>
+        <v>0.06600000051548705</v>
       </c>
     </row>
     <row r="10">
@@ -2319,13 +2319,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.0396999994336511</v>
+        <v>0.03380000089237001</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.0700999999025953</v>
+        <v>0.06359999861160759</v>
       </c>
     </row>
     <row r="11">
@@ -2334,13 +2334,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.03879999985656468</v>
+        <v>0.03330000072310213</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.06469999971159268</v>
+        <v>0.0622000006842427</v>
       </c>
     </row>
     <row r="12">
@@ -2349,13 +2349,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.03550000019458821</v>
+        <v>0.08929999967222102</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.06430000030377414</v>
+        <v>0.06239999856916256</v>
       </c>
     </row>
     <row r="13">
@@ -2364,13 +2364,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.03590000051190145</v>
+        <v>0.03380000089237001</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.06410000059986487</v>
+        <v>0.06880000000819564</v>
       </c>
     </row>
     <row r="14">
@@ -2379,13 +2379,13 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.03569999989849748</v>
+        <v>0.03300000025774352</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.06329999996523838</v>
+        <v>0.06190000021888409</v>
       </c>
     </row>
     <row r="15">
@@ -2394,13 +2394,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.03560000004654285</v>
+        <v>0.03269999979238492</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.06940000002941815</v>
+        <v>0.06270000085351057</v>
       </c>
     </row>
     <row r="16">
@@ -2409,13 +2409,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.03540000034263358</v>
+        <v>0.03269999979238492</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.06240000038815197</v>
+        <v>0.06170000051497482</v>
       </c>
     </row>
     <row r="17">
@@ -2424,13 +2424,13 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.03530000049067894</v>
+        <v>0.03280000055383425</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.0625000002401066</v>
+        <v>0.06100000064179767</v>
       </c>
     </row>
     <row r="18">
@@ -2439,13 +2439,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.04369999987829942</v>
+        <v>0.04990000161342323</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.06339999981719302</v>
+        <v>0.0748999991628807</v>
       </c>
     </row>
     <row r="19">
@@ -2454,13 +2454,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.03550000019458821</v>
+        <v>0.03319999996165279</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.06339999981719302</v>
+        <v>0.06100000064179767</v>
       </c>
     </row>
     <row r="20">
@@ -2469,13 +2469,13 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.0352000006387243</v>
+        <v>0.03289999949629419</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.05830000009154901</v>
+        <v>0.060799999118899</v>
       </c>
     </row>
     <row r="21">
@@ -2484,13 +2484,13 @@
         <v>14</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.03539999943313887</v>
+        <v>0.03219999962311704</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.05830000009154901</v>
+        <v>0.060799999118899</v>
       </c>
     </row>
     <row r="22">
@@ -2499,13 +2499,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.03509999987727497</v>
+        <v>0.03250000008847564</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.05820000023959437</v>
+        <v>0.06059999941498972</v>
       </c>
     </row>
     <row r="23">
@@ -2514,13 +2514,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.03529999958118424</v>
+        <v>0.03189999915775843</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.06020000000717118</v>
+        <v>0.06010000106471125</v>
       </c>
     </row>
     <row r="24">
@@ -2529,13 +2529,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.03370000013092067</v>
+        <v>0.03219999962311704</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.05880000026081689</v>
+        <v>0.05989999954181258</v>
       </c>
     </row>
     <row r="25">
@@ -2544,13 +2544,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.03370000013092067</v>
+        <v>0.03199999991920777</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.06020000000717118</v>
+        <v>0.05969999983790331</v>
       </c>
     </row>
     <row r="26">
@@ -2559,13 +2559,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.03430000015214318</v>
+        <v>0.03230000038456637</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.05830000009154901</v>
+        <v>0.05979999878036324</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
@@ -2574,13 +2574,13 @@
         <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.03379999998287531</v>
+        <v>0.03219999962311704</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.05870000040886225</v>
+        <v>0.06009999924572185</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
@@ -2590,27 +2590,27 @@
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>0.03706000015881727</v>
+      </c>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="1" t="n"/>
+      <c r="F28" s="1" t="n">
+        <v>0.06329999978333944</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B29" s="19" t="n">
-        <v>0.03691000001708744</v>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Desviación Estándar</t>
+        </is>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>0.06320500006040675</v>
+        <v>0.01303135492178933</v>
       </c>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>0.00376366269709597</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.004964025685248844</v>
+      <c r="F29" s="1" t="n">
+        <v>0.005040885320423747</v>
       </c>
     </row>
   </sheetData>
@@ -2631,7 +2631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B6:F30"/>
+  <dimension ref="B6:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -2685,13 +2685,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.0608000000283937</v>
+        <v>0.06519999988086056</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.09959999988495838</v>
+        <v>0.1233000002685003</v>
       </c>
     </row>
     <row r="9">
@@ -2700,13 +2700,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.05580000015470432</v>
+        <v>0.0551999983144924</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.09229999977833359</v>
+        <v>0.09990000035031699</v>
       </c>
     </row>
     <row r="10">
@@ -2715,13 +2715,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.05080000028101495</v>
+        <v>0.1513000006525544</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.09480000062467298</v>
+        <v>0.126899998576846</v>
       </c>
     </row>
     <row r="11">
@@ -2730,13 +2730,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.05099999998492422</v>
+        <v>0.05169999894860666</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.08929999967222102</v>
+        <v>0.149200001033023</v>
       </c>
     </row>
     <row r="12">
@@ -2745,13 +2745,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.0501000004078378</v>
+        <v>0.0500999994983431</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.08729999990464421</v>
+        <v>0.1245999992534053</v>
       </c>
     </row>
     <row r="13">
@@ -2760,13 +2760,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.05150000015419209</v>
+        <v>0.05060000148660038</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.08570000045438064</v>
+        <v>0.09689999933470972</v>
       </c>
     </row>
     <row r="14">
@@ -2775,13 +2775,13 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.0501000004078378</v>
+        <v>0.05239999882178381</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.08679999973537633</v>
+        <v>0.09680000039224979</v>
       </c>
     </row>
     <row r="15">
@@ -2790,13 +2790,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.04919999992125668</v>
+        <v>0.05120000059832819</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.08609999986219918</v>
+        <v>0.09750000026542693</v>
       </c>
     </row>
     <row r="16">
@@ -2805,13 +2805,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.04940000053466065</v>
+        <v>0.05140000030223746</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.08710000020073494</v>
+        <v>0.1298999995924532</v>
       </c>
     </row>
     <row r="17">
@@ -2820,13 +2820,13 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.04960000023856992</v>
+        <v>0.05109999983687885</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.08590000015828991</v>
+        <v>0.1013000000966713</v>
       </c>
     </row>
     <row r="18">
@@ -2835,13 +2835,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.04900000021734741</v>
+        <v>0.05109999983687885</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.0853000001370674</v>
+        <v>0.09990000035031699</v>
       </c>
     </row>
     <row r="19">
@@ -2850,13 +2850,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.04809999973076629</v>
+        <v>0.051799999710056</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.08479999996779952</v>
+        <v>0.1066000004357193</v>
       </c>
     </row>
     <row r="20">
@@ -2865,13 +2865,13 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.04919999992125668</v>
+        <v>0.05240000064077321</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.09019999924930744</v>
+        <v>0.1001999989966862</v>
       </c>
     </row>
     <row r="21">
@@ -2880,13 +2880,13 @@
         <v>14</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.04879999960394343</v>
+        <v>0.2877999995689606</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.08519999937561806</v>
+        <v>0.09979999958886765</v>
       </c>
     </row>
     <row r="22">
@@ -2895,13 +2895,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.04790000002685701</v>
+        <v>0.06229999962670263</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.08550000075047137</v>
+        <v>0.1037000001815613</v>
       </c>
     </row>
     <row r="23">
@@ -2910,13 +2910,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.04780000017490238</v>
+        <v>0.05650000093737617</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.08519999937561806</v>
+        <v>0.1028000006044749</v>
       </c>
     </row>
     <row r="24">
@@ -2925,13 +2925,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.04770000032294774</v>
+        <v>0.05340000097930897</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.08639999941806309</v>
+        <v>0.1021000007312978</v>
       </c>
     </row>
     <row r="25">
@@ -2940,13 +2940,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.04900000021734741</v>
+        <v>0.08300000081362668</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.08819999948173063</v>
+        <v>0.1171999992948258</v>
       </c>
     </row>
     <row r="26">
@@ -2955,13 +2955,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.04820000049221562</v>
+        <v>0.05419999979494605</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.08479999996779952</v>
+        <v>0.1090000005206093</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
@@ -2970,13 +2970,13 @@
         <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.04769999941345304</v>
+        <v>0.05290000081004109</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.08470000011584489</v>
+        <v>0.10640000073181</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
@@ -2986,27 +2986,27 @@
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>0.07178000005296781</v>
+      </c>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="1" t="n"/>
+      <c r="F28" s="1" t="n">
+        <v>0.1097000000299886</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B29" s="19" t="n">
-        <v>0.05008500011172146</v>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Desviación Estándar</t>
+        </is>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>0.08775999990575656</v>
+        <v>0.05568956810669567</v>
       </c>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>0.003128523295129414</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.003865556410138084</v>
+      <c r="F29" s="1" t="n">
+        <v>0.01417874609007567</v>
       </c>
     </row>
   </sheetData>
@@ -3027,7 +3027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B6:F30"/>
+  <dimension ref="B6:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -3081,13 +3081,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.09310000041296007</v>
+        <v>0.1495000014983816</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.1342999994449201</v>
+        <v>0.2648000008775853</v>
       </c>
     </row>
     <row r="9">
@@ -3096,13 +3096,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.08419999994657701</v>
+        <v>0.1128000003518537</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.1285999996980536</v>
+        <v>0.2117000003636349</v>
       </c>
     </row>
     <row r="10">
@@ -3111,13 +3111,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.07890000051702373</v>
+        <v>0.1090999994630693</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.1259999999092543</v>
+        <v>0.270799999270821</v>
       </c>
     </row>
     <row r="11">
@@ -3126,13 +3126,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.07790000017848797</v>
+        <v>0.10889999975916</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.1239000002897228</v>
+        <v>0.1840000004449394</v>
       </c>
     </row>
     <row r="12">
@@ -3141,13 +3141,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.07679999998799758</v>
+        <v>0.1114000006054994</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.1227000002472778</v>
+        <v>0.1796999986254377</v>
       </c>
     </row>
     <row r="13">
@@ -3156,13 +3156,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.07819999973435188</v>
+        <v>0.1116000003094086</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.1240999999936321</v>
+        <v>0.1873000001069158</v>
       </c>
     </row>
     <row r="14">
@@ -3171,13 +3171,13 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.07819999973435188</v>
+        <v>0.1119999997172272</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.1222999999299645</v>
+        <v>0.2055999993899604</v>
       </c>
     </row>
     <row r="15">
@@ -3186,13 +3186,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.07800000003044261</v>
+        <v>0.1120000015362166</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.1229999998031417</v>
+        <v>0.1926999993884237</v>
       </c>
     </row>
     <row r="16">
@@ -3201,13 +3201,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.07670000013604295</v>
+        <v>0.11129999984405</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.1221000002260553</v>
+        <v>0.1962000005732989</v>
       </c>
     </row>
     <row r="17">
@@ -3216,13 +3216,13 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.07760000062262407</v>
+        <v>0.1281999993807403</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.121900000522146</v>
+        <v>0.202200000785524</v>
       </c>
     </row>
     <row r="18">
@@ -3231,13 +3231,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.0762999998187297</v>
+        <v>0.116699999125558</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.1210000000355649</v>
+        <v>0.2069999991363147</v>
       </c>
     </row>
     <row r="19">
@@ -3246,13 +3246,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.07650000043213367</v>
+        <v>0.1157000006060116</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.1218000006701914</v>
+        <v>0.2149000010831514</v>
       </c>
     </row>
     <row r="20">
@@ -3261,13 +3261,13 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.07589999950141646</v>
+        <v>0.1338000001851469</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.1217999997606967</v>
+        <v>0.192899999092333</v>
       </c>
     </row>
     <row r="21">
@@ -3276,13 +3276,13 @@
         <v>14</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.07610000011482043</v>
+        <v>0.1515999992989236</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.1275000004170579</v>
+        <v>0.196900000446476</v>
       </c>
     </row>
     <row r="22">
@@ -3291,13 +3291,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.07529999948019395</v>
+        <v>0.3199000002496177</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.1275000004170579</v>
+        <v>0.2015999998548068</v>
       </c>
     </row>
     <row r="23">
@@ -3306,13 +3306,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.07639999967068434</v>
+        <v>0.1315999998041661</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.1209000001836102</v>
+        <v>0.1962999995157588</v>
       </c>
     </row>
     <row r="24">
@@ -3321,13 +3321,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.08010000055946875</v>
+        <v>0.2127999996446306</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.1210999998875195</v>
+        <v>0.2160999993066071</v>
       </c>
     </row>
     <row r="25">
@@ -3336,13 +3336,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.07569999979750719</v>
+        <v>0.1515999992989236</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.1224999996338738</v>
+        <v>0.1977999982045731</v>
       </c>
     </row>
     <row r="26">
@@ -3351,13 +3351,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.07439999990310753</v>
+        <v>0.1426999988325406</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.1204000000143424</v>
+        <v>0.2110999994329177</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
@@ -3366,13 +3366,13 @@
         <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.07639999967068434</v>
+        <v>0.1439999996364349</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.1213000005009235</v>
+        <v>0.2168999999412335</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
@@ -3382,27 +3382,27 @@
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>0.139359999957378</v>
+      </c>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="1" t="n"/>
+      <c r="F28" s="1" t="n">
+        <v>0.2073249997920357</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B29" s="19" t="n">
-        <v>0.0781350000124803</v>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Desviación Estándar</t>
+        </is>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>0.1237350000792503</v>
+        <v>0.04925658276401827</v>
       </c>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>0.00409431905187294</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.003457756229237903</v>
+      <c r="F29" s="1" t="n">
+        <v>0.0232026741022374</v>
       </c>
     </row>
   </sheetData>
@@ -3423,7 +3423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B6:F30"/>
+  <dimension ref="B6:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -3477,13 +3477,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.1443999999537482</v>
+        <v>0.2198999991378514</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.1794999998310232</v>
+        <v>0.3044000004592817</v>
       </c>
     </row>
     <row r="9">
@@ -3492,13 +3492,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.111500000457454</v>
+        <v>0.2058000009128591</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.1676000001680222</v>
+        <v>0.2490000006218906</v>
       </c>
     </row>
     <row r="10">
@@ -3507,13 +3507,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.1086000002032961</v>
+        <v>0.1928000001498731</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.1656000004004454</v>
+        <v>0.2284000001964159</v>
       </c>
     </row>
     <row r="11">
@@ -3522,13 +3522,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.109100000372564</v>
+        <v>0.2220000005763723</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.1651000002311775</v>
+        <v>0.2359000009164447</v>
       </c>
     </row>
     <row r="12">
@@ -3537,13 +3537,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.1055000002452289</v>
+        <v>0.18140000065614</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.1610999997865292</v>
+        <v>0.2462000011291821</v>
       </c>
     </row>
     <row r="13">
@@ -3552,13 +3552,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.1075999998647603</v>
+        <v>0.1752999996824656</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.1623999996809289</v>
+        <v>0.2282999994349666</v>
       </c>
     </row>
     <row r="14">
@@ -3567,13 +3567,13 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.1050999999279156</v>
+        <v>0.1698999985819682</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.1621999999770196</v>
+        <v>0.5484999983309535</v>
       </c>
     </row>
     <row r="15">
@@ -3582,13 +3582,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.1073000003088964</v>
+        <v>0.1687000003585126</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.1611999996384839</v>
+        <v>0.3987000000051921</v>
       </c>
     </row>
     <row r="16">
@@ -3597,13 +3597,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.1038999998854706</v>
+        <v>0.1893000007839873</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.162100000125065</v>
+        <v>0.3063999993173638</v>
       </c>
     </row>
     <row r="17">
@@ -3612,13 +3612,13 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.10640000073181</v>
+        <v>0.168399999893154</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.1640999998926418</v>
+        <v>0.2195000015490223</v>
       </c>
     </row>
     <row r="18">
@@ -3627,13 +3627,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.1058999996530474</v>
+        <v>0.1674000013736077</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.1616999998077517</v>
+        <v>0.2086000004055677</v>
       </c>
     </row>
     <row r="19">
@@ -3642,13 +3642,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.1062999999703607</v>
+        <v>0.1628000009077368</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.1673000006121583</v>
+        <v>0.2476999998179963</v>
       </c>
     </row>
     <row r="20">
@@ -3657,13 +3657,13 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.1048999993145117</v>
+        <v>0.163500000780914</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.157999999828462</v>
+        <v>0.2043000004050555</v>
       </c>
     </row>
     <row r="21">
@@ -3672,13 +3672,13 @@
         <v>14</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.1054000003932742</v>
+        <v>0.1597000009496696</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.1586000007591792</v>
+        <v>0.2014000001508975</v>
       </c>
     </row>
     <row r="22">
@@ -3687,13 +3687,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.1048000003720517</v>
+        <v>0.1726999998936662</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.1583000002938206</v>
+        <v>0.2232999995612772</v>
       </c>
     </row>
     <row r="23">
@@ -3702,13 +3702,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.1039999997374252</v>
+        <v>0.1580999996804167</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.1597000000401749</v>
+        <v>0.2390999998169718</v>
       </c>
     </row>
     <row r="24">
@@ -3717,13 +3717,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.1026999998430256</v>
+        <v>0.1587999995535938</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.1622999998289743</v>
+        <v>0.2192000010836637</v>
       </c>
     </row>
     <row r="25">
@@ -3732,13 +3732,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.1056999999491381</v>
+        <v>0.1563000005262438</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.159199999870907</v>
+        <v>0.2170000007026829</v>
       </c>
     </row>
     <row r="26">
@@ -3747,13 +3747,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.2014000001508975</v>
+        <v>0.1499000009062001</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.1590000001669978</v>
+        <v>0.2273999998578802</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
@@ -3762,13 +3762,13 @@
         <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.1103999993574689</v>
+        <v>0.1510000001871958</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.1585999998496845</v>
+        <v>0.2273999998578802</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
@@ -3778,27 +3778,27 @@
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>0.1746850002746214</v>
+      </c>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="1" t="n"/>
+      <c r="F28" s="1" t="n">
+        <v>0.2590350001810293</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B29" s="19" t="n">
-        <v>0.1130450000346173</v>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Desviación Estándar</t>
+        </is>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>0.1626800000394724</v>
+        <v>0.02118252189811828</v>
       </c>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>0.02256806024575178</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.00492155303140847</v>
+      <c r="F29" s="1" t="n">
+        <v>0.08203469873722791</v>
       </c>
     </row>
   </sheetData>
@@ -3819,7 +3819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B6:F30"/>
+  <dimension ref="B6:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -3873,13 +3873,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.003000000106112566</v>
+        <v>0.002200000380980782</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.002900000254157931</v>
+        <v>0.002199998561991379</v>
       </c>
     </row>
     <row r="9">
@@ -3888,13 +3888,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.001500000507803634</v>
+        <v>0.001300000803894363</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.002299999323440716</v>
+        <v>0.001799999154172838</v>
       </c>
     </row>
     <row r="10">
@@ -3903,13 +3903,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.001100000190490391</v>
+        <v>0.0008000006346264854</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.002099999619531445</v>
+        <v>0.001599999450263567</v>
       </c>
     </row>
     <row r="11">
@@ -3918,13 +3918,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.001000000338535756</v>
+        <v>0.0008000006346264854</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.003900000592693686</v>
+        <v>0.00270000055024866</v>
       </c>
     </row>
     <row r="12">
@@ -3933,13 +3933,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.001200000042445026</v>
+        <v>0.0008999995770864189</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.001599999450263567</v>
+        <v>0.001200000042445026</v>
       </c>
     </row>
     <row r="13">
@@ -3948,13 +3948,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.0009999994290410541</v>
+        <v>0.0008000006346264854</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.001599999450263567</v>
+        <v>0.001200000042445026</v>
       </c>
     </row>
     <row r="14">
@@ -3963,13 +3963,13 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.001000000338535756</v>
+        <v>0.0008000006346264854</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.001499999598308932</v>
+        <v>0.001100001099985093</v>
       </c>
     </row>
     <row r="15">
@@ -3978,13 +3978,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.001000000338535756</v>
+        <v>0.0006999998731771484</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.001500000507803634</v>
+        <v>0.001099999280995689</v>
       </c>
     </row>
     <row r="16">
@@ -3993,13 +3993,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.001000000338535756</v>
+        <v>0.0008000006346264854</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.001500000507803634</v>
+        <v>0.001099999280995689</v>
       </c>
     </row>
     <row r="17">
@@ -4008,13 +4008,13 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.001000000338535756</v>
+        <v>0.0006999998731771484</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.001499999598308932</v>
+        <v>0.001200000042445026</v>
       </c>
     </row>
     <row r="18">
@@ -4023,13 +4023,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.001000000338535756</v>
+        <v>0.0007999988156370819</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.001499999598308932</v>
+        <v>0.001100001099985093</v>
       </c>
     </row>
     <row r="19">
@@ -4038,13 +4038,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.001100000190490391</v>
+        <v>0.0006999998731771484</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.001500000507803634</v>
+        <v>0.001200000042445026</v>
       </c>
     </row>
     <row r="20">
@@ -4053,13 +4053,13 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.0009999994290410541</v>
+        <v>0.0007999988156370819</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.001500000507803634</v>
+        <v>0.001200000042445026</v>
       </c>
     </row>
     <row r="21">
@@ -4068,13 +4068,13 @@
         <v>14</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.0009999994290410541</v>
+        <v>0.0006999998731771484</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.001600000359758269</v>
+        <v>0.001099999280995689</v>
       </c>
     </row>
     <row r="22">
@@ -4083,13 +4083,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.0009999994290410541</v>
+        <v>0.0007999988156370819</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.001499999598308932</v>
+        <v>0.001100001099985093</v>
       </c>
     </row>
     <row r="23">
@@ -4098,13 +4098,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.0009999994290410541</v>
+        <v>0.01909999991767108</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.001500000507803634</v>
+        <v>0.001100001099985093</v>
       </c>
     </row>
     <row r="24">
@@ -4113,13 +4113,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.0008999995770864189</v>
+        <v>0.0006999998731771484</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.001499999598308932</v>
+        <v>0.001100001099985093</v>
       </c>
     </row>
     <row r="25">
@@ -4128,13 +4128,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.0009000004865811206</v>
+        <v>0.0006999998731771484</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.001399999746354297</v>
+        <v>0.001200000042445026</v>
       </c>
     </row>
     <row r="26">
@@ -4143,13 +4143,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.001000000338535756</v>
+        <v>0.0007999988156370819</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.001500000507803634</v>
+        <v>0.001200000042445026</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
@@ -4158,13 +4158,13 @@
         <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.001000000338535756</v>
+        <v>0.0006999998731771484</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.001499999598308932</v>
+        <v>0.001200000042445026</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
@@ -4174,27 +4174,27 @@
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>0.001779999911377672</v>
+      </c>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="1" t="n"/>
+      <c r="F28" s="1" t="n">
+        <v>0.001335000069957459</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B29" s="19" t="n">
-        <v>0.001135000047725043</v>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Desviación Estándar</t>
+        </is>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>0.001769999971656944</v>
+        <v>0.004090888479126671</v>
       </c>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>0.0004568485154312257</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.000619932179075401</v>
+      <c r="F29" s="1" t="n">
+        <v>0.0004283073339262428</v>
       </c>
     </row>
   </sheetData>
@@ -4215,7 +4215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B6:F30"/>
+  <dimension ref="B6:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -4269,13 +4269,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.00399999953515362</v>
+        <v>0.00250000084633939</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.004300000000512227</v>
+        <v>0.003200000719516538</v>
       </c>
     </row>
     <row r="9">
@@ -4284,13 +4284,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.002499999936844688</v>
+        <v>0.001699998392723501</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.003299999661976472</v>
+        <v>0.002000000677071512</v>
       </c>
     </row>
     <row r="10">
@@ -4299,13 +4299,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.001799999154172838</v>
+        <v>0.001200000042445026</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.003000000106112566</v>
+        <v>0.001700000211712904</v>
       </c>
     </row>
     <row r="11">
@@ -4314,13 +4314,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.001599999450263567</v>
+        <v>0.001100001099985093</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.003000000106112566</v>
+        <v>0.001799999154172838</v>
       </c>
     </row>
     <row r="12">
@@ -4329,13 +4329,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.001599999450263567</v>
+        <v>0.001000000338535756</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.003000000106112566</v>
+        <v>0.001700000211712904</v>
       </c>
     </row>
     <row r="13">
@@ -4344,13 +4344,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.001700000211712904</v>
+        <v>0.001100001099985093</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.003000000106112566</v>
+        <v>0.001799999154172838</v>
       </c>
     </row>
     <row r="14">
@@ -4359,13 +4359,13 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.001600000359758269</v>
+        <v>0.001000000338535756</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.002999999196617864</v>
+        <v>0.001700000211712904</v>
       </c>
     </row>
     <row r="15">
@@ -4374,13 +4374,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.001600000359758269</v>
+        <v>0.001099999280995689</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.002999999196617864</v>
+        <v>0.001800000973162241</v>
       </c>
     </row>
     <row r="16">
@@ -4389,13 +4389,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.001700000211712904</v>
+        <v>0.001200000042445026</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.002799999492708594</v>
+        <v>0.001700000211712904</v>
       </c>
     </row>
     <row r="17">
@@ -4404,13 +4404,13 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.001700000211712904</v>
+        <v>0.001100001099985093</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.002900000254157931</v>
+        <v>0.001700000211712904</v>
       </c>
     </row>
     <row r="18">
@@ -4419,13 +4419,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.001600000359758269</v>
+        <v>0.001200000042445026</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.002899999344663229</v>
+        <v>0.001700000211712904</v>
       </c>
     </row>
     <row r="19">
@@ -4434,13 +4434,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.001600000359758269</v>
+        <v>0.001000000338535756</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.002799999492708594</v>
+        <v>0.001800000973162241</v>
       </c>
     </row>
     <row r="20">
@@ -4449,13 +4449,13 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.001600000359758269</v>
+        <v>0.001200000042445026</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.002900000254157931</v>
+        <v>0.001800000973162241</v>
       </c>
     </row>
     <row r="21">
@@ -4464,13 +4464,13 @@
         <v>14</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.001499999598308932</v>
+        <v>0.001099999280995689</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.002899999344663229</v>
+        <v>0.001800000973162241</v>
       </c>
     </row>
     <row r="22">
@@ -4479,13 +4479,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.001499999598308932</v>
+        <v>0.001099999280995689</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.002999999196617864</v>
+        <v>0.001700000211712904</v>
       </c>
     </row>
     <row r="23">
@@ -4494,13 +4494,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.001600000359758269</v>
+        <v>0.001099999280995689</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.002899999344663229</v>
+        <v>0.001700000211712904</v>
       </c>
     </row>
     <row r="24">
@@ -4509,13 +4509,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.001700000211712904</v>
+        <v>0.0009999985195463523</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.002899999344663229</v>
+        <v>0.001800000973162241</v>
       </c>
     </row>
     <row r="25">
@@ -4524,13 +4524,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.001699999302218203</v>
+        <v>0.001099999280995689</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.002899999344663229</v>
+        <v>0.001800000973162241</v>
       </c>
     </row>
     <row r="26">
@@ -4539,13 +4539,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.001699999302218203</v>
+        <v>0.001099999280995689</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.002899999344663229</v>
+        <v>0.001700000211712904</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
@@ -4554,13 +4554,13 @@
         <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.001700000211712904</v>
+        <v>0.001099999280995689</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.002799999492708594</v>
+        <v>0.001799999154172838</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
@@ -4570,27 +4570,27 @@
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>0.001199999860546086</v>
+      </c>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="1" t="n"/>
+      <c r="F28" s="1" t="n">
+        <v>0.001835000330174807</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B29" s="19" t="n">
-        <v>0.001799999927243334</v>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Desviación Estándar</t>
+        </is>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>0.003009999636560678</v>
+        <v>0.0003402786107520956</v>
       </c>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>0.0005572487865473137</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.0003226535731764411</v>
+      <c r="F29" s="1" t="n">
+        <v>0.0003297129087837335</v>
       </c>
     </row>
   </sheetData>
@@ -4611,7 +4611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B6:F30"/>
+  <dimension ref="B6:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -4665,13 +4665,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.00470000031782547</v>
+        <v>0.002799999492708594</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.005400000191002619</v>
+        <v>0.003299999661976472</v>
       </c>
     </row>
     <row r="9">
@@ -4680,13 +4680,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.003699999979289714</v>
+        <v>0.002000000677071512</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.00470000031782547</v>
+        <v>0.002799999492708594</v>
       </c>
     </row>
     <row r="10">
@@ -4695,13 +4695,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.002599999788799323</v>
+        <v>0.001599999450263567</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.004100000296602957</v>
+        <v>0.002400000084890053</v>
       </c>
     </row>
     <row r="11">
@@ -4710,13 +4710,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.002400000084890053</v>
+        <v>0.001500000507803634</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.003899999683198985</v>
+        <v>0.002400000084890053</v>
       </c>
     </row>
     <row r="12">
@@ -4725,13 +4725,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.002400000084890053</v>
+        <v>0.001600001269252971</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.003899999683198985</v>
+        <v>0.002400000084890053</v>
       </c>
     </row>
     <row r="13">
@@ -4740,13 +4740,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.002599999788799323</v>
+        <v>0.001599999450263567</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.004000000444648322</v>
+        <v>0.002400000084890053</v>
       </c>
     </row>
     <row r="14">
@@ -4755,13 +4755,13 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.002400000084890053</v>
+        <v>0.001599999450263567</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.003900000592693686</v>
+        <v>0.002400000084890053</v>
       </c>
     </row>
     <row r="15">
@@ -4770,13 +4770,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.002499999936844688</v>
+        <v>0.00149999868881423</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.003799999831244349</v>
+        <v>0.002400000084890053</v>
       </c>
     </row>
     <row r="16">
@@ -4785,13 +4785,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.002400000084890053</v>
+        <v>0.001500000507803634</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.003699999979289714</v>
+        <v>0.002400000084890053</v>
       </c>
     </row>
     <row r="17">
@@ -4800,13 +4800,13 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.002400000084890053</v>
+        <v>0.001500000507803634</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.003899999683198985</v>
+        <v>0.002300001142430119</v>
       </c>
     </row>
     <row r="18">
@@ -4815,13 +4815,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.002399999175395351</v>
+        <v>0.001399999746354297</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.003900000592693686</v>
+        <v>0.002299999323440716</v>
       </c>
     </row>
     <row r="19">
@@ -4830,13 +4830,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.002300000232935417</v>
+        <v>0.001599999450263567</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.003799999831244349</v>
+        <v>0.002400000084890053</v>
       </c>
     </row>
     <row r="20">
@@ -4845,13 +4845,13 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.002799999492708594</v>
+        <v>0.001700000211712904</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.003899999683198985</v>
+        <v>0.002400000084890053</v>
       </c>
     </row>
     <row r="21">
@@ -4860,13 +4860,13 @@
         <v>14</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.002599999788799323</v>
+        <v>0.001500000507803634</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.003900000592693686</v>
+        <v>0.002400000084890053</v>
       </c>
     </row>
     <row r="22">
@@ -4875,13 +4875,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.002400000084890053</v>
+        <v>0.001399999746354297</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.003899999683198985</v>
+        <v>0.002300001142430119</v>
       </c>
     </row>
     <row r="23">
@@ -4890,13 +4890,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.002499999936844688</v>
+        <v>0.001500000507803634</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.004000000444648322</v>
+        <v>0.002300001142430119</v>
       </c>
     </row>
     <row r="24">
@@ -4905,13 +4905,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.002299999323440716</v>
+        <v>0.001399999746354297</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.003899999683198985</v>
+        <v>0.002400000084890053</v>
       </c>
     </row>
     <row r="25">
@@ -4920,13 +4920,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.002400000084890053</v>
+        <v>0.001500000507803634</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.003899999683198985</v>
+        <v>0.002299999323440716</v>
       </c>
     </row>
     <row r="26">
@@ -4935,13 +4935,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.002300000232935417</v>
+        <v>0.001399999746354297</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.003900000592693686</v>
+        <v>0.002400000084890053</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
@@ -4950,13 +4950,13 @@
         <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.002400000084890053</v>
+        <v>0.001500000507803634</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.003899999683198985</v>
+        <v>0.002300001142430119</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
@@ -4966,27 +4966,27 @@
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>0.001605000034032855</v>
+      </c>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="1" t="n"/>
+      <c r="F28" s="1" t="n">
+        <v>0.00243500016949838</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B29" s="19" t="n">
-        <v>0.002624999933686922</v>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Desviación Estándar</t>
+        </is>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>0.004015000058643636</v>
+        <v>0.0003119969059264914</v>
       </c>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>0.000575714721138291</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.000380131638145025</v>
+      <c r="F29" s="1" t="n">
+        <v>0.0002300455452745264</v>
       </c>
     </row>
   </sheetData>
@@ -5007,7 +5007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B6:F30"/>
+  <dimension ref="B6:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -5061,13 +5061,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.005899999450775795</v>
+        <v>0.003400000423425809</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.006799999937356915</v>
+        <v>0.004300000000512227</v>
       </c>
     </row>
     <row r="9">
@@ -5076,13 +5076,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.003699999979289714</v>
+        <v>0.00250000084633939</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.005599999894911889</v>
+        <v>0.003499999365885742</v>
       </c>
     </row>
     <row r="10">
@@ -5091,13 +5091,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.003099999958067201</v>
+        <v>0.002099999619531445</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.004699999408330768</v>
+        <v>0.003200000719516538</v>
       </c>
     </row>
     <row r="11">
@@ -5106,13 +5106,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.002800000402203295</v>
+        <v>0.002000000677071512</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.004599999556376133</v>
+        <v>0.003000001015607268</v>
       </c>
     </row>
     <row r="12">
@@ -5121,13 +5121,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.002699999640753958</v>
+        <v>0.001899999915622175</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.00470000031782547</v>
+        <v>0.003000001015607268</v>
       </c>
     </row>
     <row r="13">
@@ -5136,13 +5136,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.003099999958067201</v>
+        <v>0.002100001438520849</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.004900000021734741</v>
+        <v>0.003299999661976472</v>
       </c>
     </row>
     <row r="14">
@@ -5151,13 +5151,13 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.002900000254157931</v>
+        <v>0.002000000677071512</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.00470000031782547</v>
+        <v>0.003200000719516538</v>
       </c>
     </row>
     <row r="15">
@@ -5166,13 +5166,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.002800000402203295</v>
+        <v>0.001899999915622175</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.004599999556376133</v>
+        <v>0.003099999958067201</v>
       </c>
     </row>
     <row r="16">
@@ -5181,13 +5181,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.002800000402203295</v>
+        <v>0.001899999915622175</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.00470000031782547</v>
+        <v>0.003199998900527135</v>
       </c>
     </row>
     <row r="17">
@@ -5196,13 +5196,13 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.003000000106112566</v>
+        <v>0.002000000677071512</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.004800000169780105</v>
+        <v>0.003199998900527135</v>
       </c>
     </row>
     <row r="18">
@@ -5211,13 +5211,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.002600000698294025</v>
+        <v>0.001800000973162241</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.004699999408330768</v>
+        <v>0.003099999958067201</v>
       </c>
     </row>
     <row r="19">
@@ -5226,13 +5226,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.002699999640753958</v>
+        <v>0.001899999915622175</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.004699999408330768</v>
+        <v>0.003000001015607268</v>
       </c>
     </row>
     <row r="20">
@@ -5241,13 +5241,13 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.002799999492708594</v>
+        <v>0.001799999154172838</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.00470000031782547</v>
+        <v>0.003099999958067201</v>
       </c>
     </row>
     <row r="21">
@@ -5256,13 +5256,13 @@
         <v>14</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.00270000055024866</v>
+        <v>0.001800000973162241</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.004600000465870835</v>
+        <v>0.003099999958067201</v>
       </c>
     </row>
     <row r="22">
@@ -5271,13 +5271,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.00270000055024866</v>
+        <v>0.001899999915622175</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.00470000031782547</v>
+        <v>0.003099999958067201</v>
       </c>
     </row>
     <row r="23">
@@ -5286,13 +5286,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.002799999492708594</v>
+        <v>0.001899999915622175</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.004499999704421498</v>
+        <v>0.003000001015607268</v>
       </c>
     </row>
     <row r="24">
@@ -5301,13 +5301,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.002699999640753958</v>
+        <v>0.001899999915622175</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.0045000006139162</v>
+        <v>0.003000001015607268</v>
       </c>
     </row>
     <row r="25">
@@ -5316,13 +5316,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.002799999492708594</v>
+        <v>0.001899999915622175</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.004600000465870835</v>
+        <v>0.002999999196617864</v>
       </c>
     </row>
     <row r="26">
@@ -5331,13 +5331,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.002800000402203295</v>
+        <v>0.001899999915622175</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.004600000465870835</v>
+        <v>0.003099999958067201</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
@@ -5346,13 +5346,13 @@
         <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.00270000055024866</v>
+        <v>0.001799999154172838</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.004599999556376133</v>
+        <v>0.003000001015607268</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
@@ -5362,27 +5362,27 @@
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>0.002020000192715088</v>
+      </c>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="1" t="n"/>
+      <c r="F28" s="1" t="n">
+        <v>0.003175000165356323</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B29" s="19" t="n">
-        <v>0.003005000053235563</v>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Desviación Estándar</t>
+        </is>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>0.004815000011149095</v>
+        <v>0.0003607012278289694</v>
       </c>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>0.0007221858548528538</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.0005203996135776998</v>
+      <c r="F29" s="1" t="n">
+        <v>0.000293571263887986</v>
       </c>
     </row>
   </sheetData>
@@ -5403,7 +5403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B6:F30"/>
+  <dimension ref="B6:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -5457,13 +5457,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.005400000191002619</v>
+        <v>0.003400000423425809</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.01090000023395987</v>
+        <v>0.004800000169780105</v>
       </c>
     </row>
     <row r="9">
@@ -5472,13 +5472,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.004300000000512227</v>
+        <v>0.002599999788799323</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.00650000038149301</v>
+        <v>0.004099998477613553</v>
       </c>
     </row>
     <row r="10">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.003600000127335079</v>
+        <v>0.002299999323440716</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.006100000064179767</v>
+        <v>0.003799999831244349</v>
       </c>
     </row>
     <row r="11">
@@ -5502,13 +5502,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.003400000423425809</v>
+        <v>0.002299999323440716</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.005799999598821159</v>
+        <v>0.003799999831244349</v>
       </c>
     </row>
     <row r="12">
@@ -5517,13 +5517,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.003299999661976472</v>
+        <v>0.002100001438520849</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.005699999746866524</v>
+        <v>0.003799999831244349</v>
       </c>
     </row>
     <row r="13">
@@ -5532,13 +5532,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.003799999831244349</v>
+        <v>0.002400000084890053</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.006100000064179767</v>
+        <v>0.003900000592693686</v>
       </c>
     </row>
     <row r="14">
@@ -5547,13 +5547,13 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.003699999979289714</v>
+        <v>0.00250000084633939</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.005899999450775795</v>
+        <v>0.004000001354143023</v>
       </c>
     </row>
     <row r="15">
@@ -5562,13 +5562,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.003399999513931107</v>
+        <v>0.002199998561991379</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.005799999598821159</v>
+        <v>0.003799999831244349</v>
       </c>
     </row>
     <row r="16">
@@ -5577,13 +5577,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.003600000127335079</v>
+        <v>0.002200000380980782</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.005900000360270496</v>
+        <v>0.003799999831244349</v>
       </c>
     </row>
     <row r="17">
@@ -5592,13 +5592,13 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.005599999894911889</v>
+        <v>0.003600000127335079</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.005800000508315861</v>
+        <v>0.003799999831244349</v>
       </c>
     </row>
     <row r="18">
@@ -5607,13 +5607,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.003500000275380444</v>
+        <v>0.002200000380980782</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.005599999894911889</v>
+        <v>0.003799999831244349</v>
       </c>
     </row>
     <row r="19">
@@ -5622,13 +5622,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.003500000275380444</v>
+        <v>0.002099999619531445</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.005599999894911889</v>
+        <v>0.003700000888784416</v>
       </c>
     </row>
     <row r="20">
@@ -5637,13 +5637,13 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.003799999831244349</v>
+        <v>0.002299999323440716</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.005699999746866524</v>
+        <v>0.003700000888784416</v>
       </c>
     </row>
     <row r="21">
@@ -5652,13 +5652,13 @@
         <v>14</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.003499999365885742</v>
+        <v>0.002100001438520849</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.005800000508315861</v>
+        <v>0.003599998308345675</v>
       </c>
     </row>
     <row r="22">
@@ -5667,13 +5667,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.003399999513931107</v>
+        <v>0.002099999619531445</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.005599999894911889</v>
+        <v>0.003600000127335079</v>
       </c>
     </row>
     <row r="23">
@@ -5682,13 +5682,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.003400000423425809</v>
+        <v>0.001999998858082108</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.005799999598821159</v>
+        <v>0.003699999069795012</v>
       </c>
     </row>
     <row r="24">
@@ -5697,13 +5697,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.003400000423425809</v>
+        <v>0.002000000677071512</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.005699999746866524</v>
+        <v>0.003699999069795012</v>
       </c>
     </row>
     <row r="25">
@@ -5712,13 +5712,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.003400000423425809</v>
+        <v>0.002099999619531445</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.005700000656361226</v>
+        <v>0.003699999069795012</v>
       </c>
     </row>
     <row r="26">
@@ -5727,13 +5727,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.003500000275380444</v>
+        <v>0.002099999619531445</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.005599999894911889</v>
+        <v>0.003600000127335079</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
@@ -5742,13 +5742,13 @@
         <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.003199999810021836</v>
+        <v>0.002200000380980782</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.005599999894911889</v>
+        <v>0.003700000888784416</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
@@ -5758,27 +5758,27 @@
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>0.002339999991818331</v>
+      </c>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="1" t="n"/>
+      <c r="F28" s="1" t="n">
+        <v>0.003819999892584747</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B29" s="19" t="n">
-        <v>0.003735000018423307</v>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Desviación Estándar</t>
+        </is>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>0.006059999986973708</v>
+        <v>0.0004272310665545498</v>
       </c>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>0.0006482973674865093</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.001160489990114559</v>
+      <c r="F29" s="1" t="n">
+        <v>0.0002627787514355857</v>
       </c>
     </row>
   </sheetData>
@@ -5799,7 +5799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B6:F30"/>
+  <dimension ref="B6:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -5853,13 +5853,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.006899999789311551</v>
+        <v>0.01089999932446517</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.008400000297115184</v>
+        <v>0.006499998562503606</v>
       </c>
     </row>
     <row r="9">
@@ -5868,13 +5868,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.005400000191002619</v>
+        <v>0.003799999831244349</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.007700000423938036</v>
+        <v>0.005300000339047983</v>
       </c>
     </row>
     <row r="10">
@@ -5883,13 +5883,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.004599999556376133</v>
+        <v>0.002900000254157931</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.007000000550760888</v>
+        <v>0.004600000465870835</v>
       </c>
     </row>
     <row r="11">
@@ -5898,13 +5898,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.004300000000512227</v>
+        <v>0.002699998731259257</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.007099999493220821</v>
+        <v>0.004499999704421498</v>
       </c>
     </row>
     <row r="12">
@@ -5913,13 +5913,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.00419999923906289</v>
+        <v>0.00270000055024866</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.006799999937356915</v>
+        <v>0.004399998942972161</v>
       </c>
     </row>
     <row r="13">
@@ -5928,13 +5928,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.004699999408330768</v>
+        <v>0.002900000254157931</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.007300000106624793</v>
+        <v>0.004600000465870835</v>
       </c>
     </row>
     <row r="14">
@@ -5943,13 +5943,13 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.004099999387108255</v>
+        <v>0.002900000254157931</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.006799999937356915</v>
+        <v>0.004600000465870835</v>
       </c>
     </row>
     <row r="15">
@@ -5958,13 +5958,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.003699999979289714</v>
+        <v>0.002799999492708594</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.006299999768089037</v>
+        <v>0.004400000761961564</v>
       </c>
     </row>
     <row r="16">
@@ -5973,13 +5973,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.003799999831244349</v>
+        <v>0.002699998731259257</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.006199999916134402</v>
+        <v>0.004400000761961564</v>
       </c>
     </row>
     <row r="17">
@@ -5988,13 +5988,13 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.004000000444648322</v>
+        <v>0.00270000055024866</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.006699999175907578</v>
+        <v>0.004499999704421498</v>
       </c>
     </row>
     <row r="18">
@@ -6003,13 +6003,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.003899999683198985</v>
+        <v>0.002599999788799323</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.006599999323952943</v>
+        <v>0.004499999704421498</v>
       </c>
     </row>
     <row r="19">
@@ -6018,13 +6018,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.003899999683198985</v>
+        <v>0.002599999788799323</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.006599999323952943</v>
+        <v>0.004399998942972161</v>
       </c>
     </row>
     <row r="20">
@@ -6033,13 +6033,13 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.004000000444648322</v>
+        <v>0.002499999027349986</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.006499999471998308</v>
+        <v>0.004399998942972161</v>
       </c>
     </row>
     <row r="21">
@@ -6048,13 +6048,13 @@
         <v>14</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.00399999953515362</v>
+        <v>0.002499999027349986</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.00650000038149301</v>
+        <v>0.004499999704421498</v>
       </c>
     </row>
     <row r="22">
@@ -6063,13 +6063,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.003899999683198985</v>
+        <v>0.002499999027349986</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.00650000038149301</v>
+        <v>0.004399998942972161</v>
       </c>
     </row>
     <row r="23">
@@ -6078,13 +6078,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.003799999831244349</v>
+        <v>0.00250000084633939</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.00670000008540228</v>
+        <v>0.04950000038661528</v>
       </c>
     </row>
     <row r="24">
@@ -6093,13 +6093,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.003799999831244349</v>
+        <v>0.002400000084890053</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.00670000008540228</v>
+        <v>0.005699999746866524</v>
       </c>
     </row>
     <row r="25">
@@ -6108,13 +6108,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.003900000592693686</v>
+        <v>0.00250000084633939</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.00650000038149301</v>
+        <v>0.004599998646881431</v>
       </c>
     </row>
     <row r="26">
@@ -6123,13 +6123,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.003699999979289714</v>
+        <v>0.002400000084890053</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.006600000233447645</v>
+        <v>0.004400000761961564</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
@@ -6138,13 +6138,13 @@
         <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.003900000592693686</v>
+        <v>0.002499999027349986</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.006399999620043673</v>
+        <v>0.004399998942972161</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
@@ -6154,27 +6154,27 @@
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>0.003099999776168261</v>
+      </c>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="1" t="n"/>
+      <c r="F28" s="1" t="n">
+        <v>0.006929999744897941</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B29" s="19" t="n">
-        <v>0.004224999884172576</v>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Desviación Estándar</t>
+        </is>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>0.006794999944759184</v>
+        <v>0.001861238879951162</v>
       </c>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>0.0007503507512558797</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.0005145004000007857</v>
+      <c r="F29" s="1" t="n">
+        <v>0.01003441985416886</v>
       </c>
     </row>
   </sheetData>
@@ -6195,7 +6195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B6:F30"/>
+  <dimension ref="B6:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -6249,13 +6249,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.01570000040373998</v>
+        <v>0.006099999154685065</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.009599999430065509</v>
+        <v>0.006899999789311551</v>
       </c>
     </row>
     <row r="9">
@@ -6264,13 +6264,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.005900000360270496</v>
+        <v>0.004599998646881431</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.00850000014906982</v>
+        <v>0.006000000212225132</v>
       </c>
     </row>
     <row r="10">
@@ -6279,13 +6279,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.004800000169780105</v>
+        <v>0.003799999831244349</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.007800000275892671</v>
+        <v>0.005800000508315861</v>
       </c>
     </row>
     <row r="11">
@@ -6294,13 +6294,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.004600000465870835</v>
+        <v>0.003600000127335079</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.007800000275892671</v>
+        <v>0.005500000042957254</v>
       </c>
     </row>
     <row r="12">
@@ -6309,13 +6309,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.004499999704421498</v>
+        <v>0.003400000423425809</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.007499999810534064</v>
+        <v>0.005500000042957254</v>
       </c>
     </row>
     <row r="13">
@@ -6324,13 +6324,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.005099999725644011</v>
+        <v>0.003800001650233753</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.008199999683711212</v>
+        <v>0.005800000508315861</v>
       </c>
     </row>
     <row r="14">
@@ -6339,13 +6339,13 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.00470000031782547</v>
+        <v>0.003499999365885742</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.007900000127847306</v>
+        <v>0.005500000042957254</v>
       </c>
     </row>
     <row r="15">
@@ -6354,13 +6354,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.0045000006139162</v>
+        <v>0.003200000719516538</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.007600000571983401</v>
+        <v>0.005500000042957254</v>
       </c>
     </row>
     <row r="16">
@@ -6369,13 +6369,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.004499999704421498</v>
+        <v>0.003299999661976472</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.007499999810534064</v>
+        <v>0.005300000339047983</v>
       </c>
     </row>
     <row r="17">
@@ -6384,13 +6384,13 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.004699999408330768</v>
+        <v>0.003299999661976472</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.007699999514443334</v>
+        <v>0.005300000339047983</v>
       </c>
     </row>
     <row r="18">
@@ -6399,13 +6399,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.004399999852466863</v>
+        <v>0.003200000719516538</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.00740000086807413</v>
+        <v>0.005300000339047983</v>
       </c>
     </row>
     <row r="19">
@@ -6414,13 +6414,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.004399999852466863</v>
+        <v>0.003299999661976472</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.007399999958579428</v>
+        <v>0.005199999577598646</v>
       </c>
     </row>
     <row r="20">
@@ -6429,13 +6429,13 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.004499999704421498</v>
+        <v>0.003200000719516538</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.01320000046689529</v>
+        <v>0.006899999789311551</v>
       </c>
     </row>
     <row r="21">
@@ -6444,13 +6444,13 @@
         <v>14</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.004200000148557592</v>
+        <v>0.003300001480965875</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.007399999958579428</v>
+        <v>0.005300000339047983</v>
       </c>
     </row>
     <row r="22">
@@ -6459,13 +6459,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.004200000148557592</v>
+        <v>0.003299999661976472</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.007300000106624793</v>
+        <v>0.00529999852005858</v>
       </c>
     </row>
     <row r="23">
@@ -6474,13 +6474,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.004400000761961564</v>
+        <v>0.003200000719516538</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.007300000106624793</v>
+        <v>0.005300000339047983</v>
       </c>
     </row>
     <row r="24">
@@ -6489,13 +6489,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.004300000000512227</v>
+        <v>0.003200000719516538</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.007300000106624793</v>
+        <v>0.005300000339047983</v>
       </c>
     </row>
     <row r="25">
@@ -6504,13 +6504,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.004399999852466863</v>
+        <v>0.003200000719516538</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.007300000106624793</v>
+        <v>0.005199999577598646</v>
       </c>
     </row>
     <row r="26">
@@ -6519,13 +6519,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.004300000000512227</v>
+        <v>0.003200000719516538</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.007399999958579428</v>
+        <v>0.00529999852005858</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
@@ -6534,13 +6534,13 @@
         <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.004399999852466863</v>
+        <v>0.003200000719516538</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.007200000254670158</v>
+        <v>0.005199999577598646</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
@@ -6550,27 +6550,27 @@
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>0.003545000254234765</v>
+      </c>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="1" t="n"/>
+      <c r="F28" s="1" t="n">
+        <v>0.005569999939325498</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B29" s="19" t="n">
-        <v>0.005125000052430551</v>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Desviación Estándar</t>
+        </is>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>0.007965000077092554</v>
+        <v>0.0006901368855192857</v>
       </c>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>0.002517700582977758</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.001352298262640238</v>
+      <c r="F29" s="1" t="n">
+        <v>0.000504818932771369</v>
       </c>
     </row>
   </sheetData>
@@ -6591,7 +6591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B6:F30"/>
+  <dimension ref="B6:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -6645,13 +6645,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.007599999662488699</v>
+        <v>0.006000000212225132</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.01020000036078272</v>
+        <v>0.008200000593205914</v>
       </c>
     </row>
     <row r="9">
@@ -6660,13 +6660,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.006299999768089037</v>
+        <v>0.004600000465870835</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.009600000339560211</v>
+        <v>0.007099999493220821</v>
       </c>
     </row>
     <row r="10">
@@ -6675,13 +6675,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.005500000042957254</v>
+        <v>0.00399999953515362</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.008900000466383062</v>
+        <v>0.006599999323952943</v>
       </c>
     </row>
     <row r="11">
@@ -6690,13 +6690,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.005099999725644011</v>
+        <v>0.003600000127335079</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.008600000001024455</v>
+        <v>0.006399999620043673</v>
       </c>
     </row>
     <row r="12">
@@ -6705,13 +6705,13 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.004900000021734741</v>
+        <v>0.003600000127335079</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.00850000014906982</v>
+        <v>0.006099999154685065</v>
       </c>
     </row>
     <row r="13">
@@ -6720,13 +6720,13 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.005500000042957254</v>
+        <v>0.003900000592693686</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.016900000446185</v>
+        <v>0.006299998858594336</v>
       </c>
     </row>
     <row r="14">
@@ -6735,13 +6735,13 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.005299999429553282</v>
+        <v>0.003799999831244349</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.008799999704933725</v>
+        <v>0.006199999916134402</v>
       </c>
     </row>
     <row r="15">
@@ -6750,13 +6750,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.005200000487093348</v>
+        <v>0.003499999365885742</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.008399999387620483</v>
+        <v>0.006100000973674469</v>
       </c>
     </row>
     <row r="16">
@@ -6765,13 +6765,13 @@
         <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.005200000487093348</v>
+        <v>0.003499999365885742</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.008499999239575118</v>
+        <v>0.006000000212225132</v>
       </c>
     </row>
     <row r="17">
@@ -6780,13 +6780,13 @@
         <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.005099999725644011</v>
+        <v>0.003400000423425809</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.008600000001024455</v>
+        <v>0.005999998393235728</v>
       </c>
     </row>
     <row r="18">
@@ -6795,13 +6795,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0.004999999873689376</v>
+        <v>0.003399998604436405</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.008300000445160549</v>
+        <v>0.006000000212225132</v>
       </c>
     </row>
     <row r="19">
@@ -6810,13 +6810,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.004900000021734741</v>
+        <v>0.003400000423425809</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.008399999387620483</v>
+        <v>0.006000000212225132</v>
       </c>
     </row>
     <row r="20">
@@ -6825,13 +6825,13 @@
         <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.004900000021734741</v>
+        <v>0.003300001480965875</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.008299999535665847</v>
+        <v>0.006000000212225132</v>
       </c>
     </row>
     <row r="21">
@@ -6840,13 +6840,13 @@
         <v>14</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.004900000021734741</v>
+        <v>0.003400000423425809</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.00850000014906982</v>
+        <v>0.005900001269765198</v>
       </c>
     </row>
     <row r="22">
@@ -6855,13 +6855,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.004900000021734741</v>
+        <v>0.003399998604436405</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.008199999683711212</v>
+        <v>0.006000000212225132</v>
       </c>
     </row>
     <row r="23">
@@ -6870,13 +6870,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.004900000021734741</v>
+        <v>0.003400000423425809</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.008300000445160549</v>
+        <v>0.006000000212225132</v>
       </c>
     </row>
     <row r="24">
@@ -6885,13 +6885,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.004900000021734741</v>
+        <v>0.003400000423425809</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.008300000445160549</v>
+        <v>0.005899999450775795</v>
       </c>
     </row>
     <row r="25">
@@ -6900,13 +6900,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.004999999873689376</v>
+        <v>0.003399998604436405</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>18</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.008400000297115184</v>
+        <v>0.005899999450775795</v>
       </c>
     </row>
     <row r="26">
@@ -6915,13 +6915,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.004800000169780105</v>
+        <v>0.003400000423425809</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.008400000297115184</v>
+        <v>0.005799998689326458</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
@@ -6930,13 +6930,13 @@
         <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.004900000021734741</v>
+        <v>0.003400000423425809</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.008400000297115184</v>
+        <v>0.005800000508315861</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
@@ -6946,27 +6946,27 @@
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>0.003689999994094251</v>
+      </c>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="1" t="n"/>
+      <c r="F28" s="1" t="n">
+        <v>0.006214999848452862</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B29" s="19" t="n">
-        <v>0.005239999973127851</v>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Desviación Estándar</t>
+        </is>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>0.009025000053952681</v>
+        <v>0.0006239940005649962</v>
       </c>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="1" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" t="n">
-        <v>0.0006532508916277946</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.001915552805205358</v>
+      <c r="F29" s="1" t="n">
+        <v>0.0005575086158054294</v>
       </c>
     </row>
   </sheetData>
